--- a/kits/security-questionnaire/templates/answer_library.xlsx
+++ b/kits/security-questionnaire/templates/answer_library.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1. Answers are statements the client makes to its customers. Write only what the client's documents or written confirmations say. Never invent a control, a date, a number or a certification.</t>
+          <t>1. Answers are statements the client makes to its customers. Write only what the client's documents or written answers say. Never invent a control, a date, a number or a certification.</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2. Every answer cites its source (document and section, or a dated written confirmation). If the documents are silent, leave the answer blank and set Status to NEEDS CLIENT INPUT.</t>
+          <t>2. Every answer cites its source (document and section, or the client's dated written answers). If the documents are silent, leave the answer blank and set Status to NEEDS CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The client document the answer comes from (title and version), or 'Written confirmation from &lt;name&gt;, &lt;date&gt;'.</t>
+          <t>The client document the answer comes from (title and version), or 'Written answers from &lt;name&gt;, &lt;date&gt;'.</t>
         </is>
       </c>
     </row>
